--- a/project/outputs_xlsx_solution/test_new4.4-wide.xlsx
+++ b/project/outputs_xlsx_solution/test_new4.4-wide.xlsx
@@ -77,7 +77,10 @@
     <t>fmul F3, F1, F1</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
   </si>
   <si>
     <t>fadd F2, F2, F3</t>
@@ -89,10 +92,13 @@
     <t>addi X3, X3, 1</t>
   </si>
   <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
-    <t>EX</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>IS</t>
   </si>
   <si>
     <t>slt X5, X3, X2</t>
@@ -101,6 +107,12 @@
     <t>bne X5, X0, 28</t>
   </si>
   <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
     <t>fsd F2, 200(X0)</t>
   </si>
   <si>
@@ -113,13 +125,31 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -573,6 +603,15 @@
       <c r="AF1">
         <v>29</v>
       </c>
+      <c r="AG1">
+        <v>30</v>
+      </c>
+      <c r="AH1">
+        <v>31</v>
+      </c>
+      <c r="AI1">
+        <v>32</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -594,7 +633,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -614,13 +653,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -640,13 +679,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -666,13 +708,25 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -695,10 +749,10 @@
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -718,22 +772,22 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -753,19 +807,22 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -785,22 +842,25 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="M9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -811,7 +871,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -820,19 +880,19 @@
         <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -843,7 +903,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -852,16 +912,16 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -881,16 +941,16 @@
         <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -901,7 +961,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -910,16 +970,16 @@
         <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -930,7 +990,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -939,16 +999,16 @@
         <v>9</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K14" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="P14" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -959,7 +1019,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -968,16 +1028,16 @@
         <v>9</v>
       </c>
       <c r="I15" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L15" t="s">
-        <v>18</v>
-      </c>
-      <c r="O15" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="P15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -997,22 +1057,22 @@
         <v>9</v>
       </c>
       <c r="N16" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1023,7 +1083,7 @@
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L17" t="s">
         <v>5</v>
@@ -1032,19 +1092,19 @@
         <v>9</v>
       </c>
       <c r="N17" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="S17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="T17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="U17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1055,7 +1115,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L18" t="s">
         <v>5</v>
@@ -1064,16 +1124,16 @@
         <v>9</v>
       </c>
       <c r="N18" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1093,16 +1153,16 @@
         <v>9</v>
       </c>
       <c r="N19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="P19" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1113,7 +1173,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M20" t="s">
         <v>5</v>
@@ -1122,16 +1182,16 @@
         <v>9</v>
       </c>
       <c r="O20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P20" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1142,7 +1202,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M21" t="s">
         <v>5</v>
@@ -1151,62 +1211,62 @@
         <v>9</v>
       </c>
       <c r="O21" t="s">
-        <v>14</v>
-      </c>
-      <c r="U21" t="s">
-        <v>19</v>
-      </c>
-      <c r="V21" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>15</v>
+      </c>
+      <c r="R21" t="s">
+        <v>15</v>
+      </c>
+      <c r="S21" t="s">
+        <v>14</v>
+      </c>
+      <c r="T21" t="s">
+        <v>19</v>
+      </c>
+      <c r="W21" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="M22" t="s">
+        <v>5</v>
       </c>
       <c r="N22" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O22" t="s">
-        <v>9</v>
-      </c>
-      <c r="P22" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>19</v>
-      </c>
-      <c r="R22" t="s">
-        <v>19</v>
-      </c>
-      <c r="S22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T22" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="U22" t="s">
-        <v>18</v>
-      </c>
-      <c r="V22" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="W22" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N23" t="s">
         <v>5</v>
@@ -1215,27 +1275,36 @@
         <v>9</v>
       </c>
       <c r="P23" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>15</v>
+      </c>
+      <c r="R23" t="s">
+        <v>15</v>
+      </c>
+      <c r="S23" t="s">
+        <v>14</v>
+      </c>
+      <c r="T23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U23" t="s">
         <v>14</v>
       </c>
       <c r="V23" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="W23" t="s">
-        <v>19</v>
-      </c>
-      <c r="X23" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
@@ -1247,27 +1316,30 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>19</v>
-      </c>
-      <c r="R24" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="W24" t="s">
+        <v>14</v>
+      </c>
+      <c r="X24" t="s">
+        <v>14</v>
       </c>
       <c r="Y24" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="N25" t="s">
         <v>5</v>
@@ -1276,56 +1348,56 @@
         <v>9</v>
       </c>
       <c r="P25" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" t="s">
         <v>14</v>
       </c>
       <c r="R25" t="s">
         <v>19</v>
       </c>
-      <c r="S25" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>18</v>
+      <c r="Z25" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="N26" t="s">
+        <v>5</v>
       </c>
       <c r="O26" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P26" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="R26" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S26" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O27" t="s">
         <v>5</v>
@@ -1334,97 +1406,91 @@
         <v>9</v>
       </c>
       <c r="Q27" t="s">
-        <v>14</v>
-      </c>
-      <c r="V27" t="s">
-        <v>19</v>
-      </c>
-      <c r="W27" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="R27" t="s">
+        <v>14</v>
+      </c>
+      <c r="S27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B28">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="O28" t="s">
+        <v>5</v>
       </c>
       <c r="P28" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="s">
-        <v>9</v>
-      </c>
-      <c r="R28" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="S28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="U28" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V28" t="s">
         <v>19</v>
       </c>
-      <c r="W28" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>18</v>
+      <c r="AA28" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="O29" t="s">
+        <v>5</v>
       </c>
       <c r="P29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q29" t="s">
-        <v>9</v>
-      </c>
-      <c r="R29" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z29" t="s">
+        <v>21</v>
+      </c>
+      <c r="V29" t="s">
+        <v>14</v>
+      </c>
+      <c r="W29" t="s">
         <v>19</v>
       </c>
       <c r="AA29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB29" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P30" t="s">
         <v>5</v>
@@ -1433,27 +1499,45 @@
         <v>9</v>
       </c>
       <c r="R30" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="S30" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T30" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="U30" t="s">
+        <v>15</v>
+      </c>
+      <c r="V30" t="s">
+        <v>15</v>
+      </c>
+      <c r="W30" t="s">
+        <v>14</v>
+      </c>
+      <c r="X30" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
         <v>32</v>
       </c>
-      <c r="B31">
-        <v>40</v>
-      </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P31" t="s">
         <v>5</v>
@@ -1461,185 +1545,185 @@
       <c r="Q31" t="s">
         <v>9</v>
       </c>
-      <c r="R31" t="s">
-        <v>14</v>
-      </c>
-      <c r="T31" t="s">
-        <v>19</v>
-      </c>
-      <c r="U31" t="s">
-        <v>18</v>
+      <c r="S31" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>14</v>
       </c>
       <c r="AB31" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
       </c>
+      <c r="P32" t="s">
+        <v>5</v>
+      </c>
       <c r="Q32" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" t="s">
         <v>9</v>
       </c>
       <c r="S32" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="T32" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="U32" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB32" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="P33" t="s">
+        <v>5</v>
       </c>
       <c r="Q33" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="S33" t="s">
+        <v>25</v>
+      </c>
+      <c r="T33" t="s">
+        <v>25</v>
+      </c>
+      <c r="U33" t="s">
+        <v>25</v>
       </c>
       <c r="V33" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="W33" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X33" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB33" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B34">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>5</v>
       </c>
       <c r="R34" t="s">
-        <v>5</v>
-      </c>
-      <c r="S34" t="s">
         <v>9</v>
       </c>
       <c r="V34" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="W34" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X34" t="s">
         <v>19</v>
       </c>
-      <c r="Y34" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB34" t="s">
-        <v>18</v>
+      <c r="AD34" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>5</v>
       </c>
       <c r="R35" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" t="s">
         <v>9</v>
       </c>
       <c r="V35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC35" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD35" t="s">
+        <v>21</v>
+      </c>
+      <c r="X35" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y35" t="s">
         <v>19</v>
       </c>
       <c r="AE35" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>23</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>5</v>
       </c>
       <c r="R36" t="s">
-        <v>5</v>
-      </c>
-      <c r="S36" t="s">
         <v>9</v>
       </c>
       <c r="V36" t="s">
-        <v>14</v>
-      </c>
-      <c r="X36" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y36" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>19</v>
       </c>
       <c r="AE36" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R37" t="s">
         <v>5</v>
@@ -1648,62 +1732,86 @@
         <v>9</v>
       </c>
       <c r="W37" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="X37" t="s">
+        <v>15</v>
       </c>
       <c r="Y37" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z37" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>14</v>
       </c>
       <c r="AE37" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="R38" t="s">
+        <v>5</v>
       </c>
       <c r="S38" t="s">
-        <v>5</v>
-      </c>
-      <c r="T38" t="s">
         <v>9</v>
       </c>
       <c r="W38" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE38" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="R39" t="s">
+        <v>5</v>
       </c>
       <c r="S39" t="s">
-        <v>5</v>
-      </c>
-      <c r="T39" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="W39" t="s">
+        <v>21</v>
+      </c>
+      <c r="X39" t="s">
+        <v>15</v>
       </c>
       <c r="Y39" t="s">
         <v>14</v>
@@ -1711,111 +1819,244 @@
       <c r="Z39" t="s">
         <v>19</v>
       </c>
-      <c r="AA39" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE39" t="s">
-        <v>18</v>
+      <c r="AH39" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="R40" t="s">
+        <v>5</v>
       </c>
       <c r="S40" t="s">
-        <v>5</v>
-      </c>
-      <c r="T40" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="W40" t="s">
+        <v>25</v>
+      </c>
+      <c r="X40" t="s">
+        <v>25</v>
       </c>
       <c r="Y40" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>21</v>
       </c>
       <c r="AA40" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AB40" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE40" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>44</v>
+      </c>
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+      <c r="S41" t="s">
+        <v>5</v>
+      </c>
+      <c r="T41" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="S42" t="s">
+        <v>5</v>
+      </c>
+      <c r="T42" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="S43" t="s">
+        <v>5</v>
+      </c>
+      <c r="T43" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B41">
+      <c r="B44">
         <v>56</v>
       </c>
-      <c r="C41" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB41" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC41" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD41" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE41" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF41" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" t="s">
-        <v>25</v>
+      <c r="C44" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF44" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/project/outputs_xlsx_solution/test_new4.4-wide.xlsx
+++ b/project/outputs_xlsx_solution/test_new4.4-wide.xlsx
@@ -107,34 +107,34 @@
     <t>bne X5, X0, 28</t>
   </si>
   <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>fsd F2, 200(X0)</t>
+  </si>
+  <si>
+    <t>[Legend]</t>
+  </si>
+  <si>
+    <t>Instruction Fetch</t>
+  </si>
+  <si>
+    <t>Instruction Decode</t>
+  </si>
+  <si>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
     <t>RS Stall</t>
-  </si>
-  <si>
-    <t>ROB Stall</t>
-  </si>
-  <si>
-    <t>fsd F2, 200(X0)</t>
-  </si>
-  <si>
-    <t>[Legend]</t>
-  </si>
-  <si>
-    <t>Instruction Fetch</t>
-  </si>
-  <si>
-    <t>Instruction Decode</t>
-  </si>
-  <si>
-    <t>Add to Issue Queue</t>
-  </si>
-  <si>
-    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
-  </si>
-  <si>
-    <t>Write Back</t>
-  </si>
-  <si>
-    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
   </si>
   <si>
     <t>Reservation Station Stall (stalled because reservation stations are full)</t>
@@ -609,9 +609,6 @@
       <c r="AH1">
         <v>31</v>
       </c>
-      <c r="AI1">
-        <v>32</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1057,7 +1054,7 @@
         <v>9</v>
       </c>
       <c r="N16" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O16" t="s">
         <v>14</v>
@@ -1069,9 +1066,6 @@
         <v>14</v>
       </c>
       <c r="R16" t="s">
-        <v>14</v>
-      </c>
-      <c r="S16" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1094,6 +1088,9 @@
       <c r="N17" t="s">
         <v>21</v>
       </c>
+      <c r="R17" t="s">
+        <v>14</v>
+      </c>
       <c r="S17" t="s">
         <v>14</v>
       </c>
@@ -1101,9 +1098,6 @@
         <v>14</v>
       </c>
       <c r="U17" t="s">
-        <v>14</v>
-      </c>
-      <c r="V17" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1124,15 +1118,12 @@
         <v>9</v>
       </c>
       <c r="N18" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O18" t="s">
-        <v>14</v>
-      </c>
-      <c r="P18" t="s">
-        <v>19</v>
-      </c>
-      <c r="V18" t="s">
+        <v>19</v>
+      </c>
+      <c r="U18" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1155,13 +1146,13 @@
       <c r="N19" t="s">
         <v>21</v>
       </c>
+      <c r="O19" t="s">
+        <v>14</v>
+      </c>
       <c r="P19" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>19</v>
-      </c>
-      <c r="V19" t="s">
+        <v>19</v>
+      </c>
+      <c r="U19" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1182,15 +1173,12 @@
         <v>9</v>
       </c>
       <c r="O20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P20" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>19</v>
-      </c>
-      <c r="V20" t="s">
+        <v>19</v>
+      </c>
+      <c r="U20" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1213,19 +1201,13 @@
       <c r="O21" t="s">
         <v>21</v>
       </c>
+      <c r="P21" t="s">
+        <v>14</v>
+      </c>
       <c r="Q21" t="s">
-        <v>15</v>
-      </c>
-      <c r="R21" t="s">
-        <v>15</v>
-      </c>
-      <c r="S21" t="s">
-        <v>14</v>
-      </c>
-      <c r="T21" t="s">
-        <v>19</v>
-      </c>
-      <c r="W21" t="s">
+        <v>19</v>
+      </c>
+      <c r="V21" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1248,13 +1230,13 @@
       <c r="O22" t="s">
         <v>21</v>
       </c>
-      <c r="T22" t="s">
-        <v>14</v>
-      </c>
-      <c r="U22" t="s">
-        <v>19</v>
-      </c>
-      <c r="W22" t="s">
+      <c r="Q22" t="s">
+        <v>14</v>
+      </c>
+      <c r="R22" t="s">
+        <v>19</v>
+      </c>
+      <c r="V22" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1275,13 +1257,13 @@
         <v>9</v>
       </c>
       <c r="P23" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q23" t="s">
         <v>15</v>
       </c>
       <c r="R23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S23" t="s">
         <v>14</v>
@@ -1293,9 +1275,6 @@
         <v>14</v>
       </c>
       <c r="V23" t="s">
-        <v>14</v>
-      </c>
-      <c r="W23" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1318,6 +1297,9 @@
       <c r="P24" t="s">
         <v>21</v>
       </c>
+      <c r="V24" t="s">
+        <v>14</v>
+      </c>
       <c r="W24" t="s">
         <v>14</v>
       </c>
@@ -1325,9 +1307,6 @@
         <v>14</v>
       </c>
       <c r="Y24" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z24" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1348,7 +1327,7 @@
         <v>9</v>
       </c>
       <c r="P25" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q25" t="s">
         <v>14</v>
@@ -1356,7 +1335,7 @@
       <c r="R25" t="s">
         <v>19</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="Y25" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1385,7 +1364,7 @@
       <c r="S26" t="s">
         <v>19</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="Y26" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1406,7 +1385,7 @@
         <v>9</v>
       </c>
       <c r="Q27" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="R27" t="s">
         <v>14</v>
@@ -1414,7 +1393,7 @@
       <c r="S27" t="s">
         <v>19</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="Y27" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1441,15 +1420,12 @@
         <v>15</v>
       </c>
       <c r="T28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U28" t="s">
-        <v>14</v>
-      </c>
-      <c r="V28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA28" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z28" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1472,13 +1448,13 @@
       <c r="Q29" t="s">
         <v>21</v>
       </c>
+      <c r="U29" t="s">
+        <v>14</v>
+      </c>
       <c r="V29" t="s">
-        <v>14</v>
-      </c>
-      <c r="W29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA29" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z29" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1499,10 +1475,10 @@
         <v>9</v>
       </c>
       <c r="R30" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S30" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="T30" t="s">
         <v>15</v>
@@ -1511,7 +1487,7 @@
         <v>15</v>
       </c>
       <c r="V30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W30" t="s">
         <v>14</v>
@@ -1523,9 +1499,6 @@
         <v>14</v>
       </c>
       <c r="Z30" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA30" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1545,8 +1518,11 @@
       <c r="Q31" t="s">
         <v>9</v>
       </c>
-      <c r="S31" t="s">
-        <v>21</v>
+      <c r="R31" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>14</v>
       </c>
       <c r="AA31" t="s">
         <v>14</v>
@@ -1555,9 +1531,6 @@
         <v>14</v>
       </c>
       <c r="AC31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD31" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1577,16 +1550,16 @@
       <c r="Q32" t="s">
         <v>9</v>
       </c>
+      <c r="R32" t="s">
+        <v>15</v>
+      </c>
       <c r="S32" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T32" t="s">
-        <v>14</v>
-      </c>
-      <c r="U32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC32" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1606,25 +1579,22 @@
       <c r="Q33" t="s">
         <v>9</v>
       </c>
+      <c r="R33" t="s">
+        <v>24</v>
+      </c>
       <c r="S33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U33" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="V33" t="s">
-        <v>21</v>
-      </c>
-      <c r="W33" t="s">
-        <v>14</v>
-      </c>
-      <c r="X33" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD33" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC33" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1644,16 +1614,13 @@
       <c r="R34" t="s">
         <v>9</v>
       </c>
+      <c r="U34" t="s">
+        <v>14</v>
+      </c>
       <c r="V34" t="s">
-        <v>21</v>
-      </c>
-      <c r="W34" t="s">
-        <v>14</v>
-      </c>
-      <c r="X34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD34" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC34" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1673,16 +1640,16 @@
       <c r="R35" t="s">
         <v>9</v>
       </c>
+      <c r="U35" t="s">
+        <v>21</v>
+      </c>
       <c r="V35" t="s">
-        <v>21</v>
-      </c>
-      <c r="X35" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE35" t="s">
+        <v>14</v>
+      </c>
+      <c r="W35" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD35" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1702,16 +1669,16 @@
       <c r="R36" t="s">
         <v>9</v>
       </c>
-      <c r="V36" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE36" t="s">
+      <c r="U36" t="s">
+        <v>21</v>
+      </c>
+      <c r="W36" t="s">
+        <v>14</v>
+      </c>
+      <c r="X36" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD36" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1731,8 +1698,11 @@
       <c r="S37" t="s">
         <v>9</v>
       </c>
+      <c r="V37" t="s">
+        <v>15</v>
+      </c>
       <c r="W37" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="X37" t="s">
         <v>15</v>
@@ -1741,7 +1711,7 @@
         <v>15</v>
       </c>
       <c r="Z37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA37" t="s">
         <v>14</v>
@@ -1753,9 +1723,6 @@
         <v>14</v>
       </c>
       <c r="AD37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE37" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1775,8 +1742,11 @@
       <c r="S38" t="s">
         <v>9</v>
       </c>
-      <c r="W38" t="s">
-        <v>21</v>
+      <c r="V38" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>14</v>
       </c>
       <c r="AE38" t="s">
         <v>14</v>
@@ -1785,9 +1755,6 @@
         <v>14</v>
       </c>
       <c r="AG38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH38" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1807,19 +1774,16 @@
       <c r="S39" t="s">
         <v>9</v>
       </c>
+      <c r="V39" t="s">
+        <v>15</v>
+      </c>
       <c r="W39" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="X39" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z39" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH39" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG39" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1839,25 +1803,22 @@
       <c r="S40" t="s">
         <v>9</v>
       </c>
+      <c r="V40" t="s">
+        <v>24</v>
+      </c>
       <c r="W40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y40" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Z40" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA40" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH40" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG40" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1877,16 +1838,13 @@
       <c r="T41" t="s">
         <v>9</v>
       </c>
+      <c r="Y41" t="s">
+        <v>14</v>
+      </c>
       <c r="Z41" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA41" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB41" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH41" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG41" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1906,16 +1864,16 @@
       <c r="T42" t="s">
         <v>9</v>
       </c>
+      <c r="Y42" t="s">
+        <v>21</v>
+      </c>
       <c r="Z42" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB42" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC42" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI42" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH42" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1935,16 +1893,16 @@
       <c r="T43" t="s">
         <v>9</v>
       </c>
-      <c r="Z43" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC43" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD43" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI43" t="s">
+      <c r="Y43" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH43" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1956,27 +1914,27 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>9</v>
       </c>
       <c r="AD44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF44" t="s">
-        <v>21</v>
+        <v>21</v>
+      </c>
+      <c r="AG44" t="s">
+        <v>14</v>
       </c>
       <c r="AH44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI44" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
@@ -1984,7 +1942,7 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -1992,7 +1950,7 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
@@ -2000,7 +1958,7 @@
         <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -2008,7 +1966,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
@@ -2016,7 +1974,7 @@
         <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
@@ -2024,12 +1982,12 @@
         <v>20</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
         <v>34</v>
@@ -2037,7 +1995,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B54" t="s">
         <v>35</v>
